--- a/Web/TestCasesWeb/PanelControl.xlsx
+++ b/Web/TestCasesWeb/PanelControl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510CF0CA-3C4A-433B-B38C-40E7D80D6A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="2460" windowWidth="26850" windowHeight="8040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -215,54 +215,6 @@
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
         </patternFill>
       </fill>
     </dxf>
@@ -681,32 +633,18 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="PTE">
+  <conditionalFormatting sqref="G2:G5">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="BL">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="KO">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G5">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
-      <formula>NOT(ISERROR(SEARCH("PTE",G3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
-      <formula>NOT(ISERROR(SEARCH("BL",G3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
-      <formula>NOT(ISERROR(SEARCH("KO",G3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>

--- a/Web/TestCasesWeb/PanelControl.xlsx
+++ b/Web/TestCasesWeb/PanelControl.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510CF0CA-3C4A-433B-B38C-40E7D80D6A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DB64A8-D419-48FC-AD82-82EBCF29B689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Num</t>
   </si>
@@ -49,9 +49,6 @@
     <t>1. The Control Panel page is correctly.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1nAERQz7NylVKp3-O6VJW9tZcGmua-6H9/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>KO</t>
   </si>
   <si>
@@ -59,25 +56,19 @@
   </si>
   <si>
     <t>CP002</t>
-  </si>
-  <si>
-    <t>CP003</t>
-  </si>
-  <si>
-    <t>CP004</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks the opcion control panel
 </t>
   </si>
   <si>
-    <t>The user does not have the correct path. The "tenant" world must be translated.</t>
-  </si>
-  <si>
     <t>pte</t>
   </si>
   <si>
-    <t>The Control Panel home.</t>
+    <t>The user does not have the correct path. The "tenant" world must be translated: 1-controlpanel.jpg</t>
+  </si>
+  <si>
+    <t>Control Panel home</t>
   </si>
 </sst>
 </file>
@@ -175,12 +166,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -521,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -557,30 +546,28 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="7" t="s">
         <v>9</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -588,52 +575,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="8" t="s">
-        <v>17</v>
+      <c r="G3" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
@@ -647,9 +602,6 @@
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{41914BFF-B514-43B0-9CC4-3D5312038FE5}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Web/TestCasesWeb/PanelControl.xlsx
+++ b/Web/TestCasesWeb/PanelControl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DB64A8-D419-48FC-AD82-82EBCF29B689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAC2600-E783-46F0-AAF8-4122C9015A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,17 +65,30 @@
     <t>pte</t>
   </si>
   <si>
-    <t>The user does not have the correct path. The "tenant" world must be translated: 1-controlpanel.jpg</t>
-  </si>
-  <si>
     <t>Control Panel home</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The user does not have the correct path. The "tenant" world must be translated: 1-controlpanel.jpg
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14/05/26: Falta poner el path como en el resto de la aplicación: PANCON001.jpg</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +118,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -169,7 +189,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -554,7 +576,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>12</v>
@@ -567,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">

--- a/Web/TestCasesWeb/PanelControl.xlsx
+++ b/Web/TestCasesWeb/PanelControl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAC2600-E783-46F0-AAF8-4122C9015A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BB3164-3C4D-4900-B8FB-E8BAFAFABDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Num</t>
   </si>
@@ -53,19 +53,10 @@
   </si>
   <si>
     <t>CP001</t>
-  </si>
-  <si>
-    <t>CP002</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks the opcion control panel
 </t>
-  </si>
-  <si>
-    <t>pte</t>
-  </si>
-  <si>
-    <t>Control Panel home</t>
   </si>
   <si>
     <r>
@@ -83,12 +74,15 @@
       <t>14/05/26: Falta poner el path como en el resto de la aplicación: PANCON001.jpg</t>
     </r>
   </si>
+  <si>
+    <t>Control Panel page</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,14 +101,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -162,11 +148,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -183,9 +168,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -193,8 +175,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -532,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -576,41 +557,25 @@
         <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G3">
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="G2">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/Web/TestCasesWeb/PanelControl.xlsx
+++ b/Web/TestCasesWeb/PanelControl.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BB3164-3C4D-4900-B8FB-E8BAFAFABDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA8CA6D-9271-496A-A9B1-24238E652462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,6 +57,9 @@
   <si>
     <t xml:space="preserve">1. The user clicks the opcion control panel
 </t>
+  </si>
+  <si>
+    <t>Control Panel page</t>
   </si>
   <si>
     <r>
@@ -71,11 +74,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>14/05/26: Falta poner el path como en el resto de la aplicación: PANCON001.jpg</t>
+      <t>14/05/26: Falta poner el path como en el resto de la aplicación: PANCON001.jpg
+22/05/26: que sentido tiene poner el ID: PANCON002.jpg</t>
     </r>
-  </si>
-  <si>
-    <t>Control Panel page</t>
   </si>
 </sst>
 </file>
@@ -549,7 +550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -557,7 +558,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>
@@ -570,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
